--- a/artfynd/A 54189-2025 artfynd.xlsx
+++ b/artfynd/A 54189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1155,121 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130293823</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58506</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ÅVPR13, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484569</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6316539</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tjureda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54189-2025 artfynd.xlsx
+++ b/artfynd/A 54189-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>130293823</v>
       </c>
       <c r="B6" t="n">
-        <v>58506</v>
+        <v>58532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54189-2025 artfynd.xlsx
+++ b/artfynd/A 54189-2025 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>130293823</v>
       </c>
       <c r="B6" t="n">
-        <v>58532</v>
+        <v>58534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54189-2025 artfynd.xlsx
+++ b/artfynd/A 54189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89405896</v>
+        <v>121771809</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +710,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484568.8744260908</v>
+        <v>484569</v>
       </c>
       <c r="R2" t="n">
-        <v>6316539.487950112</v>
+        <v>6316539</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,42 +780,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89788504</v>
+        <v>105342151</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -851,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484568.8744260908</v>
+        <v>484569</v>
       </c>
       <c r="R3" t="n">
-        <v>6316539.487950112</v>
+        <v>6316539</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-12-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-12-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105342149</v>
+        <v>89788504</v>
       </c>
       <c r="B4" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484568.8744260908</v>
+        <v>484569</v>
       </c>
       <c r="R4" t="n">
-        <v>6316539.487950112</v>
+        <v>6316539</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,22 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,42 +998,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121771809</v>
+        <v>130293823</v>
       </c>
       <c r="B5" t="n">
-        <v>57809</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1125,12 +1071,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,42 +1113,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130293823</v>
+        <v>89405896</v>
       </c>
       <c r="B6" t="n">
-        <v>58544</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1230,22 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:10</t>
+          <t>2020-12-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2020-12-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1219,115 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105342149</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ÅVPR13, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484569</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6316539</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tjureda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-12-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-12-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54189-2025 artfynd.xlsx
+++ b/artfynd/A 54189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121771809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105342151</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89788504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130293823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89405896</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,8 +1358,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105342149</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>